--- a/rootFolder/subTest-2/Scenario-GetAllUser200/Main.rvl.xlsx
+++ b/rootFolder/subTest-2/Scenario-GetAllUser200/Main.rvl.xlsx
@@ -7,13 +7,15 @@
   </bookViews>
   <sheets>
     <sheet name="RVL" sheetId="1" r:id="rId2"/>
+    <sheet name="CreateUser" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="366" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="665" uniqueCount="115">
   <si>
     <t>Flow</t>
   </si>
@@ -235,6 +237,129 @@
   </si>
   <si>
     <t>And check location field present or not</t>
+  </si>
+  <si>
+    <t>RVL</t>
+  </si>
+  <si>
+    <t>DoPlaySheet</t>
+  </si>
+  <si>
+    <t>sheetName</t>
+  </si>
+  <si>
+    <t>CreateUser</t>
+  </si>
+  <si>
+    <t>resp</t>
+  </si>
+  <si>
+    <t>postUserData</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>When Post request sent</t>
+  </si>
+  <si>
+    <t>PostUserMap</t>
+  </si>
+  <si>
+    <t>8863869972</t>
+  </si>
+  <si>
+    <t>Rows</t>
+  </si>
+  <si>
+    <t>Shahana S</t>
+  </si>
+  <si>
+    <t>TVM</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sambit Sahu</t>
+  </si>
+  <si>
+    <t>Odisha</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>S Chandrakanth</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>of Map</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
+    <t>varr</t>
+  </si>
+  <si>
+    <t>newVar</t>
+  </si>
+  <si>
+    <t>Then validate</t>
+  </si>
+  <si>
+    <t>Then validate post field</t>
+  </si>
+  <si>
+    <t>AssertEqual</t>
+  </si>
+  <si>
+    <t>newVar.name</t>
+  </si>
+  <si>
+    <t>Shahana</t>
+  </si>
+  <si>
+    <t>Loop</t>
+  </si>
+  <si>
+    <t>Loop body</t>
+  </si>
+  <si>
+    <t>of Loop</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>apiResponse.name</t>
+  </si>
+  <si>
+    <t>resposne.location</t>
+  </si>
+  <si>
+    <t>Then assert status code 201</t>
+  </si>
+  <si>
+    <t>AssertNotNull</t>
+  </si>
+  <si>
+    <t>apiResponse.StatusCode</t>
+  </si>
+  <si>
+    <t>Then assert status code 200</t>
   </si>
 </sst>
 </file>
@@ -255,7 +380,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="203">
+  <borders count="712">
     <border>
       <left/>
       <right/>
@@ -465,11 +590,520 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="712">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -673,6 +1307,515 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="200" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="201" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="202" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="205" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="207" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="208" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="210" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="211" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="212" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="213" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="217" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="218" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="219" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="220" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="221" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="226" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="228" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="232" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="234" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="236" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="257" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="263" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="265" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="274" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="279" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="280" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="293" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="311" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="312" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="314" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="321" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="331" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="339" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="341" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="343" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="371" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="372" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="374" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="386" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="387" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="388" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="389" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="390" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="391" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="395" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="396" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="397" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="398" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="399" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="400" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="401" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="402" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="403" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="404" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="405" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="406" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="407" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="408" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="409" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="410" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="411" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="412" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="413" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="414" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="415" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="416" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="417" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="418" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="419" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="420" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="421" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="422" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="423" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="424" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="425" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="426" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="427" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="428" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="429" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="430" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="431" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="432" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="433" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="434" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="435" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="436" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="437" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="438" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="439" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="440" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="441" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="442" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="443" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="444" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="445" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="446" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="447" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="448" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="449" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="450" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="451" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="452" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="453" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="454" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="455" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="456" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="457" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="458" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="459" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="460" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="461" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="462" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="463" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="464" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="465" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="466" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="467" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="468" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="469" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="470" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="471" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="472" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="473" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="474" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="475" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="476" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="477" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="478" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="479" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="480" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="481" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="482" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="483" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="484" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="485" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="486" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="487" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="488" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="489" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="490" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="491" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="492" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="493" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="494" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="495" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="496" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="497" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="498" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="499" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="500" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="501" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="502" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="503" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="504" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="505" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="506" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="507" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="508" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="509" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="510" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="511" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="512" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="513" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="514" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="515" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="516" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="517" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="518" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="519" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="520" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="521" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="522" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="523" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="524" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="525" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="526" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="527" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="528" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="529" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="530" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="531" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="532" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="533" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="534" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="535" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="536" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="537" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="538" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="539" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="540" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="541" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="542" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="543" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="544" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="545" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="546" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="547" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="548" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="549" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="550" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="551" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="552" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="553" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="554" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="555" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="556" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="557" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="558" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="559" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="560" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="561" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="562" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="563" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="564" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="565" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="566" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="567" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="568" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="569" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="570" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="571" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="572" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="573" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="574" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="575" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="576" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="577" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="578" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="579" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="580" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="581" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="582" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="583" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="584" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="585" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="586" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="587" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="588" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="589" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="590" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="591" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="592" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="593" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="594" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="595" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="596" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="597" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="598" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="599" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="600" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="601" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="602" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="603" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="604" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="605" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="606" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="607" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="608" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="609" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="610" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="611" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="612" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="613" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="614" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="615" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="616" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="617" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="618" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="619" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="620" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="621" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="622" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="623" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="624" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="625" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="626" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="627" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="628" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="629" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="630" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="631" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="632" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="633" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="634" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="635" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="636" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="637" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="638" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="639" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="640" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="641" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="642" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="643" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="644" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="645" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="646" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="647" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="648" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="649" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="650" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="651" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="652" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="653" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="654" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="655" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="656" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="657" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="658" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="659" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="660" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="661" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="662" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="663" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="664" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="665" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="666" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="667" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="668" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="669" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="670" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="671" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="672" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="673" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="674" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="675" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="676" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="677" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="678" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="679" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="680" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="681" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="682" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="683" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="684" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="685" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="686" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="687" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="688" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="689" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="690" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="691" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="692" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="693" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="694" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="695" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="696" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="697" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="698" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="699" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="700" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="701" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="702" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="703" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="704" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="705" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="706" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="707" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="708" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="709" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="710" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="711" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,7 +1825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.34375" customWidth="true"/>
@@ -783,326 +1926,918 @@
         <v>3</v>
       </c>
       <c r="C6" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="64"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="687"/>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="692"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="688"/>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F9" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G9" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="64"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="73"/>
+      <c r="B10" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="75"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="80"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="88"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="90" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="91" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="96"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="97" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="98" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="102" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="104"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="165"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="166" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="707"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="710" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="709"/>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="708"/>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="200"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="105" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="106" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="107"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="112"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="170"/>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="169"/>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="201"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="121" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="122" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="124"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="128"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="129"/>
+      <c r="B26" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="131" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="133" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="134" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="135" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="136"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="176"/>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="177"/>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="202"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="145" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="146" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="147"/>
+      <c r="D30" s="148"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="150"/>
+      <c r="G30" s="151"/>
+      <c r="H30" s="152"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="153"/>
+      <c r="B31" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="155" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="156" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="157" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="158" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="159" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="160"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="179"/>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <tableParts/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.34375" customWidth="true"/>
+    <col min="2" max="2" width="8.4375" customWidth="true"/>
+    <col min="3" max="3" width="12.4296875" customWidth="true"/>
+    <col min="4" max="4" width="12.4296875" customWidth="true"/>
+    <col min="5" max="5" width="12.4296875" customWidth="true"/>
+    <col min="6" max="6" width="12.4296875" customWidth="true"/>
+    <col min="7" max="7" width="12.4296875" customWidth="true"/>
+    <col min="8" max="8" width="10.34765625" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="427" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="428" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="429" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="430" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="431" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="432" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="433" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="434" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="435"/>
+      <c r="B2" s="436"/>
+      <c r="C2" s="437"/>
+      <c r="D2" s="438"/>
+      <c r="E2" s="439"/>
+      <c r="F2" s="440"/>
+      <c r="G2" s="441"/>
+      <c r="H2" s="442"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="683" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="682"/>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="681"/>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="680"/>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="72"/>
+      <c r="A7" s="679"/>
+      <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="73"/>
-      <c r="B8" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="75"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="80"/>
+      <c r="A8" s="678" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="443"/>
+      <c r="B9" s="444"/>
+      <c r="C9" s="445"/>
+      <c r="D9" s="446"/>
+      <c r="E9" s="447"/>
+      <c r="F9" s="448"/>
+      <c r="G9" s="449"/>
+      <c r="H9" s="450"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="697" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="698" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="88"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="89"/>
-      <c r="B10" s="90" t="s">
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="699"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="677" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="676"/>
+      <c r="B14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C14" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D14" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F14" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="95" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="96"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="97"/>
-      <c r="B11" s="98" t="s">
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="675"/>
+      <c r="B15" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="101" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="102" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="103" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="104"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="165"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="166"/>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="200"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="105" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="106" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="107"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="170"/>
+      <c r="A16" s="674"/>
       <c r="B16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="169"/>
+      <c r="A17" s="673"/>
       <c r="B17" t="s">
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="201"/>
+      <c r="A18" s="672"/>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="121" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="122" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="123" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="124"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="128"/>
+      <c r="A19" s="671"/>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="129"/>
-      <c r="B20" s="130" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="131" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="133" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="134" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="135" t="s">
-        <v>51</v>
-      </c>
-      <c r="H20" s="136"/>
+      <c r="A20" s="483"/>
+      <c r="B20" s="484"/>
+      <c r="C20" s="485"/>
+      <c r="D20" s="486"/>
+      <c r="E20" s="487"/>
+      <c r="F20" s="488"/>
+      <c r="G20" s="489"/>
+      <c r="H20" s="490"/>
     </row>
     <row r="21">
-      <c r="A21" s="176"/>
+      <c r="A21" s="702" t="s">
+        <v>60</v>
+      </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="177"/>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" t="s">
-        <v>52</v>
-      </c>
+      <c r="A22" s="491"/>
+      <c r="B22" s="492"/>
+      <c r="C22" s="493"/>
+      <c r="D22" s="494"/>
+      <c r="E22" s="495"/>
+      <c r="F22" s="496"/>
+      <c r="G22" s="497"/>
+      <c r="H22" s="498"/>
     </row>
     <row r="23">
-      <c r="A23" s="202"/>
+      <c r="A23" s="499"/>
+      <c r="B23" s="500"/>
+      <c r="C23" s="501"/>
+      <c r="D23" s="502"/>
+      <c r="E23" s="503"/>
+      <c r="F23" s="504"/>
+      <c r="G23" s="505"/>
+      <c r="H23" s="506"/>
     </row>
     <row r="24">
-      <c r="A24" s="145" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="146" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="152"/>
+      <c r="A24" s="507"/>
+      <c r="B24" s="508"/>
+      <c r="C24" s="509"/>
+      <c r="D24" s="510"/>
+      <c r="E24" s="511"/>
+      <c r="F24" s="512"/>
+      <c r="G24" s="513"/>
+      <c r="H24" s="514"/>
     </row>
     <row r="25">
-      <c r="A25" s="153"/>
-      <c r="B25" s="154" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="155" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="156" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="157" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="158" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="159" t="s">
-        <v>55</v>
-      </c>
-      <c r="H25" s="160"/>
+      <c r="A25" s="515"/>
+      <c r="B25" s="516"/>
+      <c r="C25" s="517"/>
+      <c r="D25" s="518"/>
+      <c r="E25" s="519"/>
+      <c r="F25" s="520"/>
+      <c r="G25" s="521"/>
+      <c r="H25" s="522"/>
     </row>
     <row r="26">
-      <c r="A26" s="179"/>
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>56</v>
-      </c>
+      <c r="A26" s="523"/>
+      <c r="B26" s="524"/>
+      <c r="C26" s="525"/>
+      <c r="D26" s="526"/>
+      <c r="E26" s="527"/>
+      <c r="F26" s="528"/>
+      <c r="G26" s="529"/>
+      <c r="H26" s="530"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="531"/>
+      <c r="B27" s="532"/>
+      <c r="C27" s="533"/>
+      <c r="D27" s="534"/>
+      <c r="E27" s="535"/>
+      <c r="F27" s="536"/>
+      <c r="G27" s="537"/>
+      <c r="H27" s="538"/>
     </row>
     <row r="28">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" t="s">
-        <v>55</v>
-      </c>
+      <c r="A28" s="539"/>
+      <c r="B28" s="540"/>
+      <c r="C28" s="541"/>
+      <c r="D28" s="542"/>
+      <c r="E28" s="543"/>
+      <c r="F28" s="544"/>
+      <c r="G28" s="545"/>
+      <c r="H28" s="546"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="547"/>
+      <c r="B29" s="548"/>
+      <c r="C29" s="549"/>
+      <c r="D29" s="550"/>
+      <c r="E29" s="551"/>
+      <c r="F29" s="552"/>
+      <c r="G29" s="553"/>
+      <c r="H29" s="554"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="555"/>
+      <c r="B30" s="556"/>
+      <c r="C30" s="557"/>
+      <c r="D30" s="558"/>
+      <c r="E30" s="559"/>
+      <c r="F30" s="560"/>
+      <c r="G30" s="561"/>
+      <c r="H30" s="562"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="563"/>
+      <c r="B31" s="564"/>
+      <c r="C31" s="565"/>
+      <c r="D31" s="566"/>
+      <c r="E31" s="567"/>
+      <c r="F31" s="568"/>
+      <c r="G31" s="569"/>
+      <c r="H31" s="570"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="571"/>
+      <c r="B32" s="572"/>
+      <c r="C32" s="573"/>
+      <c r="D32" s="574"/>
+      <c r="E32" s="575"/>
+      <c r="F32" s="576"/>
+      <c r="G32" s="577"/>
+      <c r="H32" s="578"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="579"/>
+      <c r="B33" s="580"/>
+      <c r="C33" s="581"/>
+      <c r="D33" s="582"/>
+      <c r="E33" s="583"/>
+      <c r="F33" s="584"/>
+      <c r="G33" s="585"/>
+      <c r="H33" s="586"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="587"/>
+      <c r="B34" s="588"/>
+      <c r="C34" s="589"/>
+      <c r="D34" s="590"/>
+      <c r="E34" s="591"/>
+      <c r="F34" s="592"/>
+      <c r="G34" s="593"/>
+      <c r="H34" s="594"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="595"/>
+      <c r="B35" s="596"/>
+      <c r="C35" s="597"/>
+      <c r="D35" s="598"/>
+      <c r="E35" s="599"/>
+      <c r="F35" s="600"/>
+      <c r="G35" s="601"/>
+      <c r="H35" s="602"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="603"/>
+      <c r="B36" s="604"/>
+      <c r="C36" s="605"/>
+      <c r="D36" s="606"/>
+      <c r="E36" s="607"/>
+      <c r="F36" s="608"/>
+      <c r="G36" s="609"/>
+      <c r="H36" s="610"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="611"/>
+      <c r="B37" s="612"/>
+      <c r="C37" s="613"/>
+      <c r="D37" s="614"/>
+      <c r="E37" s="615"/>
+      <c r="F37" s="616"/>
+      <c r="G37" s="617"/>
+      <c r="H37" s="618"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="619"/>
+      <c r="B38" s="620"/>
+      <c r="C38" s="621"/>
+      <c r="D38" s="622"/>
+      <c r="E38" s="623"/>
+      <c r="F38" s="624"/>
+      <c r="G38" s="625"/>
+      <c r="H38" s="626"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="627"/>
+      <c r="B39" s="628"/>
+      <c r="C39" s="629"/>
+      <c r="D39" s="630"/>
+      <c r="E39" s="631"/>
+      <c r="F39" s="632"/>
+      <c r="G39" s="633"/>
+      <c r="H39" s="634"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="635"/>
+      <c r="B40" s="636"/>
+      <c r="C40" s="637"/>
+      <c r="D40" s="638"/>
+      <c r="E40" s="639"/>
+      <c r="F40" s="640"/>
+      <c r="G40" s="641"/>
+      <c r="H40" s="642"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="643"/>
+      <c r="B41" s="644"/>
+      <c r="C41" s="645"/>
+      <c r="D41" s="646"/>
+      <c r="E41" s="647"/>
+      <c r="F41" s="648"/>
+      <c r="G41" s="649"/>
+      <c r="H41" s="650"/>
     </row>
   </sheetData>
   <tableParts/>
